--- a/График времени матрицы.xlsx
+++ b/График времени матрицы.xlsx
@@ -1,36 +1,56 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B25255E-1ED7-4718-ACE5-F0AD59C8947F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7DD43F2-30CB-4706-8690-1E98B22CD07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames>
+    <definedName name="Практические_Данные" localSheetId="0">Лист1!$A$1</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Размер матрицы</t>
   </si>
   <si>
-    <t>Время (сек)</t>
+    <t>O(n^3)</t>
+  </si>
+  <si>
+    <t>Практические данные</t>
+  </si>
+  <si>
+    <t>Теоретические данные</t>
   </si>
 </sst>
 </file>
@@ -38,7 +58,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -71,7 +91,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -103,85 +123,91 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
         <a:effectLst/>
+        <a:sp3d/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
     <c:plotArea>
       <c:layout>
         <c:manualLayout>
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="3.0078988941548184E-2"/>
-          <c:y val="0.19060524717383712"/>
+          <c:x val="8.1600511753584362E-2"/>
+          <c:y val="0.20158602146470186"/>
           <c:w val="0.92484465508162195"/>
           <c:h val="0.74935061106525369"/>
         </c:manualLayout>
       </c:layout>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
+      <c:line3DChart>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Лист1!$A$1</c:f>
+              <c:f>Лист1!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Размер матрицы</c:v>
+                  <c:v>Практические данные</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
+            <a:sp3d/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="2.948920484465508E-2"/>
-                  <c:y val="-0.32141275883780795"/>
+                  <c:x val="-7.3686711759509815E-3"/>
+                  <c:y val="-0.34886463092588388"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -202,8 +228,8 @@
               <c:idx val="1"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="2.5276461295418641E-2"/>
-                  <c:y val="-0.26136861707689879"/>
+                  <c:x val="1.4526207720924974E-2"/>
+                  <c:y val="-0.31352705070776971"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -224,8 +250,8 @@
               <c:idx val="2"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="1.0531858873091101E-2"/>
-                  <c:y val="-0.2013244753159896"/>
+                  <c:x val="7.4603321440383187E-3"/>
+                  <c:y val="-0.27818947048965553"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -246,8 +272,8 @@
               <c:idx val="3"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0.12848867825171142"/>
-                  <c:y val="-0.28962468378791484"/>
+                  <c:x val="-2.201423163500554E-2"/>
+                  <c:y val="-0.23472119037856012"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -268,8 +294,8 @@
               <c:idx val="4"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="4.8446550816219021E-2"/>
-                  <c:y val="-0.22251652534925179"/>
+                  <c:x val="-2.8340652304432948E-2"/>
+                  <c:y val="-0.21428106693631391"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -290,8 +316,8 @@
               <c:idx val="5"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="1.0531858873091101E-2"/>
-                  <c:y val="-0.19072845029935856"/>
+                  <c:x val="-2.7861790254794572E-2"/>
+                  <c:y val="-0.20170923026276114"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -374,7 +400,10 @@
                   <c:spPr>
                     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
                       <a:solidFill>
-                        <a:schemeClr val="accent2"/>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
                       </a:solidFill>
                       <a:round/>
                     </a:ln>
@@ -384,7 +413,7 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
-          <c:xVal>
+          <c:cat>
             <c:numRef>
               <c:f>Лист1!$A$2:$A$8</c:f>
               <c:numCache>
@@ -413,8 +442,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
               <c:f>Лист1!$B$2:$B$8</c:f>
               <c:numCache>
@@ -443,11 +472,423 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
+          </c:val>
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-2C58-4454-A223-2FDB2B09D113}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Теоретические данные</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="4.9143822467941335E-2"/>
+                  <c:y val="-0.4145219509443091"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{E000F273-2E93-4DF7-A15E-2BBB5D510861}" type="VALUE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[ЗНАЧЕНИЕ]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-8FFE-4AD8-8035-8FE6698C76C5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="2.6107655686093835E-2"/>
+                  <c:y val="-0.36785391673203577"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{31456C1C-D5CC-4F7F-BF3D-F186BE10998A}" type="VALUE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[ЗНАЧЕНИЕ]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-8FFE-4AD8-8035-8FE6698C76C5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="5.6822544728557141E-2"/>
+                  <c:y val="-0.28000820527363929"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{438F1FB7-7577-45AC-8996-8ABC39FDDB00}" type="VALUE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[ЗНАЧЕНИЕ]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-8FFE-4AD8-8035-8FE6698C76C5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.0750211164862166E-2"/>
+                  <c:y val="-0.16471070898449364"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{EFD8A19E-BC79-46BD-A8D5-7C567967A019}" type="YVALUE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[ЗНАЧЕНИЕ Y]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-8FFE-4AD8-8035-8FE6698C76C5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.8428933425478002E-2"/>
+                  <c:y val="-0.14823963808604426"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t> </a:t>
+                    </a:r>
+                    <a:fld id="{CDB5F7F1-6733-495B-9EBD-2599F47ED2CE}" type="YVALUE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[ЗНАЧЕНИЕ Y]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" baseline="0"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-8FFE-4AD8-8035-8FE6698C76C5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-4.6072333563694945E-2"/>
+                  <c:y val="-0.23883052802751575"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{496DC371-A78A-453E-AB3D-D0C805E36C12}" type="YVALUE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[ЗНАЧЕНИЕ Y]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-8FFE-4AD8-8035-8FE6698C76C5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{964371AA-25A7-44A3-A5CA-0D16991E1C42}" type="YVALUE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[ЗНАЧЕНИЕ Y]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="ru-RU"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-8FFE-4AD8-8035-8FE6698C76C5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Лист1!$A$2:$A$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$D$2:$D$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>9.9999999999999992E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.79999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.3999999999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6400</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>100000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8FFE-4AD8-8035-8FE6698C76C5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -461,15 +902,29 @@
         </c:dLbls>
         <c:axId val="1398606767"/>
         <c:axId val="1398604367"/>
-      </c:scatterChart>
-      <c:valAx>
+        <c:axId val="36230736"/>
+      </c:line3DChart>
+      <c:catAx>
         <c:axId val="1398606767"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="10000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -509,23 +964,112 @@
         </c:txPr>
         <c:crossAx val="1398604367"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
       <c:valAx>
         <c:axId val="1398604367"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="0.000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="1398606767"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
+      <c:serAx>
+        <c:axId val="36230736"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1398604367"/>
+      </c:serAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -535,7 +1079,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="t"/>
+      <c:legendPos val="b"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -606,6 +1150,7 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
+  <c:userShapes r:id="rId3"/>
 </c:chartSpace>
 </file>
 
@@ -1169,16 +1714,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>90487</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>75246</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>449580</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>129539</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1203,7 +1748,223 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>358140</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38173D73-4C15-08C2-6B4B-995DBD3CF423}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11811000" y="3977640"/>
+          <a:ext cx="1203960" cy="541020"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100">
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>___</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100"/>
+            <a:t> - </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>T(n)</a:t>
+          </a:r>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100">
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>___</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t> - </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100"/>
+            <a:t>Программа</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0</cdr:x>
+      <cdr:y>0.23574</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.18152</cdr:x>
+      <cdr:y>0.2868</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66C3655D-02B5-8AB4-54A8-9B0FCA3AE1F1}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="1090614"/>
+          <a:ext cx="1501140" cy="236220"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200"/>
+            <a:t>Y</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100" kern="1200" baseline="0"/>
+            <a:t> - Время(Сек)</a:t>
+          </a:r>
+          <a:endParaRPr lang="ru-RU" sz="1100" kern="1200"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.25266</cdr:x>
+      <cdr:y>0.82647</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.43985</cdr:x>
+      <cdr:y>0.88153</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDEEEC61-5850-10C8-7087-EDC1592F956C}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="360000">
+          <a:off x="2089405" y="3823481"/>
+          <a:ext cx="1548000" cy="254745"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" vert="horz" wrap="square" lIns="216000" tIns="36000" rtlCol="0">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200"/>
+            <a:t>X</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200" baseline="0"/>
+            <a:t> - </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100" kern="1200" baseline="0"/>
+            <a:t>размер матрицы</a:t>
+          </a:r>
+          <a:endParaRPr lang="ru-RU" sz="1100" kern="1200"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1469,78 +2230,135 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="26.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>100</v>
       </c>
       <c r="B2" s="1">
         <v>3.0000000000000001E-3</v>
       </c>
+      <c r="C2">
+        <v>1000000</v>
+      </c>
+      <c r="D2">
+        <f>1*0.0000001*C2</f>
+        <v>9.9999999999999992E-2</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>200</v>
       </c>
       <c r="B3" s="1">
         <v>2.7E-2</v>
       </c>
+      <c r="C3">
+        <v>8000000</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D8" si="0">1*0.0000001*C3</f>
+        <v>0.79999999999999993</v>
+      </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>400</v>
       </c>
       <c r="B4" s="1">
         <v>0.20799999999999999</v>
       </c>
+      <c r="C4">
+        <v>64000000</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>6.3999999999999995</v>
+      </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1000</v>
       </c>
       <c r="B5" s="1">
         <v>4.0439999999999996</v>
       </c>
+      <c r="C5">
+        <v>1000000000</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2000</v>
       </c>
       <c r="B6" s="1">
         <v>41.250999999999998</v>
       </c>
+      <c r="C6">
+        <v>8000000000</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4000</v>
       </c>
       <c r="B7" s="1">
         <v>502.11799999999999</v>
       </c>
+      <c r="C7">
+        <v>64000000000</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>6400</v>
+      </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>10000</v>
       </c>
       <c r="B8" s="1">
         <v>8063.085</v>
+      </c>
+      <c r="C8">
+        <v>1000000000000</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>100000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/График времени матрицы.xlsx
+++ b/График времени матрицы.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7DD43F2-30CB-4706-8690-1E98B22CD07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F15CCFA9-20D4-4C3A-89F6-7ED415D43C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -123,58 +123,10 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:view3D>
-      <c:rotX val="15"/>
-      <c:rotY val="20"/>
-      <c:rAngAx val="0"/>
-    </c:view3D>
-    <c:floor>
-      <c:thickness val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
-      </c:spPr>
-    </c:floor>
-    <c:sideWall>
-      <c:thickness val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
-      </c:spPr>
-    </c:sideWall>
-    <c:backWall>
-      <c:thickness val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
-      </c:spPr>
-    </c:backWall>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="8.1600511753584362E-2"/>
-          <c:y val="0.20158602146470186"/>
-          <c:w val="0.92484465508162195"/>
-          <c:h val="0.74935061106525369"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:line3DChart>
+      <c:layout/>
+      <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -192,35 +144,37 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
-            <a:sp3d/>
           </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-7.3686711759509815E-3"/>
-                  <c:y val="-0.34886463092588388"/>
+                  <c:x val="-0.13975215123426027"/>
+                  <c:y val="-0.33487081741104352"/>
                 </c:manualLayout>
               </c:layout>
-              <c:showLegendKey val="0"/>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="1"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
-              <c:separator>; </c:separator>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-2C58-4454-A223-2FDB2B09D113}"/>
+                  <c16:uniqueId val="{00000010-0A35-4810-A609-63EB88A8B8B5}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -228,21 +182,21 @@
               <c:idx val="1"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="1.4526207720924974E-2"/>
-                  <c:y val="-0.31352705070776971"/>
+                  <c:x val="-0.15241037908236155"/>
+                  <c:y val="-0.34270473828844256"/>
                 </c:manualLayout>
               </c:layout>
-              <c:showLegendKey val="0"/>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="1"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
-              <c:separator>; </c:separator>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000004-2C58-4454-A223-2FDB2B09D113}"/>
+                  <c16:uniqueId val="{0000000F-0A35-4810-A609-63EB88A8B8B5}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -250,21 +204,21 @@
               <c:idx val="2"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="7.4603321440383187E-3"/>
-                  <c:y val="-0.27818947048965553"/>
+                  <c:x val="-0.14608126515831094"/>
+                  <c:y val="-0.34662169872714216"/>
                 </c:manualLayout>
               </c:layout>
-              <c:showLegendKey val="0"/>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="1"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
-              <c:separator>; </c:separator>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-2C58-4454-A223-2FDB2B09D113}"/>
+                  <c16:uniqueId val="{0000000E-0A35-4810-A609-63EB88A8B8B5}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -272,21 +226,21 @@
               <c:idx val="3"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-2.201423163500554E-2"/>
-                  <c:y val="-0.23472119037856012"/>
+                  <c:x val="-0.15030067444101133"/>
+                  <c:y val="-0.35053865916584176"/>
                 </c:manualLayout>
               </c:layout>
-              <c:showLegendKey val="0"/>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="1"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
-              <c:separator>; </c:separator>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000002-2C58-4454-A223-2FDB2B09D113}"/>
+                  <c16:uniqueId val="{0000000D-0A35-4810-A609-63EB88A8B8B5}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -294,21 +248,21 @@
               <c:idx val="4"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-2.8340652304432948E-2"/>
-                  <c:y val="-0.21428106693631391"/>
+                  <c:x val="-0.13401375460978771"/>
+                  <c:y val="-0.35837258004324085"/>
                 </c:manualLayout>
               </c:layout>
-              <c:showLegendKey val="0"/>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="1"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
-              <c:separator>; </c:separator>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000001-2C58-4454-A223-2FDB2B09D113}"/>
+                  <c16:uniqueId val="{0000000C-0A35-4810-A609-63EB88A8B8B5}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -316,21 +270,21 @@
               <c:idx val="5"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-2.7861790254794572E-2"/>
-                  <c:y val="-0.20170923026276114"/>
+                  <c:x val="-0.13249476726801562"/>
+                  <c:y val="-0.35837258004324085"/>
                 </c:manualLayout>
               </c:layout>
-              <c:showLegendKey val="0"/>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="1"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
-              <c:separator>; </c:separator>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000007-2C58-4454-A223-2FDB2B09D113}"/>
+                  <c16:uniqueId val="{0000000B-0A35-4810-A609-63EB88A8B8B5}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -338,21 +292,21 @@
               <c:idx val="6"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-2.3170089520800574E-2"/>
-                  <c:y val="-9.1832216810802295E-2"/>
+                  <c:x val="-9.1488089305292539E-3"/>
+                  <c:y val="-0.13510583503736534"/>
                 </c:manualLayout>
               </c:layout>
-              <c:showLegendKey val="0"/>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="1"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
-              <c:separator>; </c:separator>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000006-2C58-4454-A223-2FDB2B09D113}"/>
+                  <c16:uniqueId val="{0000000A-0A35-4810-A609-63EB88A8B8B5}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -386,13 +340,11 @@
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
+            <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:separator>; </c:separator>
-            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -473,10 +425,10 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2C58-4454-A223-2FDB2B09D113}"/>
+              <c16:uniqueId val="{00000001-0A35-4810-A609-63EB88A8B8B5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -495,51 +447,37 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
-            <a:sp3d/>
           </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="4.9143822467941335E-2"/>
-                  <c:y val="-0.4145219509443091"/>
+                  <c:x val="-0.1027057377321506"/>
+                  <c:y val="-0.28003337126924949"/>
                 </c:manualLayout>
               </c:layout>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{E000F273-2E93-4DF7-A15E-2BBB5D510861}" type="VALUE">
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:pPr/>
-                      <a:t>[ЗНАЧЕНИЕ]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="ru-RU"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:showLegendKey val="0"/>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="1"/>
               <c:showVal val="1"/>
-              <c:showCatName val="1"/>
+              <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000007-8FFE-4AD8-8035-8FE6698C76C5}"/>
+                  <c16:uniqueId val="{00000008-0A35-4810-A609-63EB88A8B8B5}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -547,37 +485,21 @@
               <c:idx val="1"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="2.6107655686093835E-2"/>
-                  <c:y val="-0.36785391673203577"/>
+                  <c:x val="-0.10692514701485099"/>
+                  <c:y val="-0.27611641083054994"/>
                 </c:manualLayout>
               </c:layout>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{31456C1C-D5CC-4F7F-BF3D-F186BE10998A}" type="VALUE">
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:pPr/>
-                      <a:t>[ЗНАЧЕНИЕ]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="ru-RU"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:showLegendKey val="0"/>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="1"/>
               <c:showVal val="1"/>
-              <c:showCatName val="1"/>
+              <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000006-8FFE-4AD8-8035-8FE6698C76C5}"/>
+                  <c16:uniqueId val="{00000007-0A35-4810-A609-63EB88A8B8B5}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -585,37 +507,21 @@
               <c:idx val="2"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="5.6822544728557141E-2"/>
-                  <c:y val="-0.28000820527363929"/>
+                  <c:x val="-9.8486328449450142E-2"/>
+                  <c:y val="-0.28395033170794909"/>
                 </c:manualLayout>
               </c:layout>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{438F1FB7-7577-45AC-8996-8ABC39FDDB00}" type="VALUE">
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:pPr/>
-                      <a:t>[ЗНАЧЕНИЕ]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="ru-RU"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:showLegendKey val="0"/>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="1"/>
               <c:showVal val="1"/>
-              <c:showCatName val="1"/>
+              <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-8FFE-4AD8-8035-8FE6698C76C5}"/>
+                  <c16:uniqueId val="{00000006-0A35-4810-A609-63EB88A8B8B5}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -623,37 +529,21 @@
               <c:idx val="3"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="1.0750211164862166E-2"/>
-                  <c:y val="-0.16471070898449364"/>
+                  <c:x val="-0.10092827004219417"/>
+                  <c:y val="-0.28786729214664869"/>
                 </c:manualLayout>
               </c:layout>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{EFD8A19E-BC79-46BD-A8D5-7C567967A019}" type="YVALUE">
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:pPr/>
-                      <a:t>[ЗНАЧЕНИЕ Y]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="ru-RU"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:showLegendKey val="0"/>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="1"/>
               <c:showVal val="1"/>
-              <c:showCatName val="1"/>
+              <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000004-8FFE-4AD8-8035-8FE6698C76C5}"/>
+                  <c16:uniqueId val="{00000005-0A35-4810-A609-63EB88A8B8B5}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -661,41 +551,21 @@
               <c:idx val="4"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="1.8428933425478002E-2"/>
-                  <c:y val="-0.14823963808604426"/>
+                  <c:x val="-9.4599156118143457E-2"/>
+                  <c:y val="-0.28786729214664852"/>
                 </c:manualLayout>
               </c:layout>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:r>
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:t> </a:t>
-                    </a:r>
-                    <a:fld id="{CDB5F7F1-6733-495B-9EBD-2599F47ED2CE}" type="YVALUE">
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:pPr/>
-                      <a:t>[ЗНАЧЕНИЕ Y]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-US" baseline="0"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:showLegendKey val="0"/>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="1"/>
               <c:showVal val="1"/>
-              <c:showCatName val="1"/>
+              <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-8FFE-4AD8-8035-8FE6698C76C5}"/>
+                  <c16:uniqueId val="{00000004-0A35-4810-A609-63EB88A8B8B5}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -703,69 +573,21 @@
               <c:idx val="5"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-4.6072333563694945E-2"/>
-                  <c:y val="-0.23883052802751575"/>
+                  <c:x val="-0.12472573839662456"/>
+                  <c:y val="-0.24869768775965276"/>
                 </c:manualLayout>
               </c:layout>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{496DC371-A78A-453E-AB3D-D0C805E36C12}" type="YVALUE">
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:pPr/>
-                      <a:t>[ЗНАЧЕНИЕ Y]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="ru-RU"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:showLegendKey val="0"/>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="1"/>
               <c:showVal val="1"/>
-              <c:showCatName val="1"/>
+              <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000002-8FFE-4AD8-8035-8FE6698C76C5}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="6"/>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{964371AA-25A7-44A3-A5CA-0D16991E1C42}" type="YVALUE">
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:pPr/>
-                      <a:t>[ЗНАЧЕНИЕ Y]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="ru-RU"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000008-8FFE-4AD8-8035-8FE6698C76C5}"/>
+                  <c16:uniqueId val="{00000009-0A35-4810-A609-63EB88A8B8B5}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -799,12 +621,11 @@
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="1"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -888,43 +709,93 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8FFE-4AD8-8035-8FE6698C76C5}"/>
+              <c16:uniqueId val="{00000002-0A35-4810-A609-63EB88A8B8B5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="1"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1398606767"/>
-        <c:axId val="1398604367"/>
-        <c:axId val="36230736"/>
-      </c:line3DChart>
+        <c:smooth val="0"/>
+        <c:axId val="568947856"/>
+        <c:axId val="568948816"/>
+      </c:lineChart>
       <c:catAx>
-        <c:axId val="1398606767"/>
+        <c:axId val="568947856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>X</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> - </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ru-RU" baseline="0"/>
+                  <a:t>размер матрицы</a:t>
+                </a:r>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
           <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-        </c:majorGridlines>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -934,8 +805,8 @@
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -962,15 +833,15 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1398604367"/>
+        <c:crossAx val="568948816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1398604367"/>
+        <c:axId val="568948816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -990,55 +861,72 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Y</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> - </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ru-RU" baseline="0"/>
+                  <a:t>Время(Сек)</a:t>
+                </a:r>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="0.000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1398606767"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:serAx>
-        <c:axId val="36230736"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -1068,8 +956,10 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1398604367"/>
-      </c:serAx>
+        <c:crossAx val="568947856"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -1136,7 +1026,7 @@
     <a:effectLst/>
   </c:spPr>
   <c:txPr>
-    <a:bodyPr/>
+    <a:bodyPr anchor="ctr" anchorCtr="1"/>
     <a:lstStyle/>
     <a:p>
       <a:pPr>
@@ -1150,7 +1040,6 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
-  <c:userShapes r:id="rId3"/>
 </c:chartSpace>
 </file>
 
@@ -1195,7 +1084,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1222,8 +1111,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1303,6 +1192,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -1313,6 +1207,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -1324,7 +1223,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -1344,6 +1243,9 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1356,10 +1258,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -1399,23 +1301,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -1520,8 +1421,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1653,20 +1554,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -1680,17 +1580,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -1714,23 +1603,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>75246</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>449580</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>129539</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="19" name="Диаграмма 18">
+        <xdr:cNvPr id="2" name="Диаграмма 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BEB713A-89AD-899E-5181-6C2EB2F05F45}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17EE68B5-BA39-D383-17A6-2762C783A783}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1748,223 +1637,7 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>358140</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="TextBox 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38173D73-4C15-08C2-6B4B-995DBD3CF423}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11811000" y="3977640"/>
-          <a:ext cx="1203960" cy="541020"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1100">
-              <a:ln>
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>___</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1100"/>
-            <a:t> - </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>T(n)</a:t>
-          </a:r>
-          <a:endParaRPr lang="ru-RU" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1100">
-              <a:ln>
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>___</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t> - </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1100"/>
-            <a:t>Программа</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0</cdr:x>
-      <cdr:y>0.23574</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.18152</cdr:x>
-      <cdr:y>0.2868</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="2" name="TextBox 1">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66C3655D-02B5-8AB4-54A8-9B0FCA3AE1F1}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="1090614"/>
-          <a:ext cx="1501140" cy="236220"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="square" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200"/>
-            <a:t>Y</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1100" kern="1200" baseline="0"/>
-            <a:t> - Время(Сек)</a:t>
-          </a:r>
-          <a:endParaRPr lang="ru-RU" sz="1100" kern="1200"/>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.25266</cdr:x>
-      <cdr:y>0.82647</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.43985</cdr:x>
-      <cdr:y>0.88153</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="3" name="TextBox 2">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDEEEC61-5850-10C8-7087-EDC1592F956C}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="360000">
-          <a:off x="2089405" y="3823481"/>
-          <a:ext cx="1548000" cy="254745"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" vert="horz" wrap="square" lIns="216000" tIns="36000" rtlCol="0">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200"/>
-            <a:t>X</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200" baseline="0"/>
-            <a:t> - </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1100" kern="1200" baseline="0"/>
-            <a:t>размер матрицы</a:t>
-          </a:r>
-          <a:endParaRPr lang="ru-RU" sz="1100" kern="1200"/>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-</c:userShapes>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
